--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E740F2F0-17DB-F94B-A5DD-C3874060258B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA9A7A5-A7CA-F045-ACED-36F1F6D6994E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -131,9 +131,6 @@
     <t>documentNo, lineNo</t>
   </si>
   <si>
-    <t>documentNo, lineNo, company</t>
-  </si>
-  <si>
     <t>code, description, company, source_system</t>
   </si>
   <si>
@@ -149,9 +146,6 @@
     <t>Entity</t>
   </si>
   <si>
-    <t>entryno, vendorNo, company</t>
-  </si>
-  <si>
     <t>entryno,itemno,company,source_system</t>
   </si>
   <si>
@@ -170,9 +164,6 @@
     <t>document no,  line no.</t>
   </si>
   <si>
-    <t>city, postcode, county, countryregion, basecalendarcode, shipmentbincode, receiptbincode, adjustmentbincode, putawaybinpolicy, pickbinpolicy, bincapacitycode, pickbinpolicy</t>
-  </si>
-  <si>
     <t>accounttype, globaldimenson1code, globaldimenson2code, accountcategory</t>
   </si>
   <si>
@@ -270,6 +261,15 @@
   </si>
   <si>
     <t>jobtitle</t>
+  </si>
+  <si>
+    <t>postcode, county, countryregioncode</t>
+  </si>
+  <si>
+    <t>documentno, lineno, company</t>
+  </si>
+  <si>
+    <t>entryno, vendorno, company</t>
   </si>
 </sst>
 </file>
@@ -714,22 +714,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>72</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>76</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -740,7 +740,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -757,7 +757,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -774,16 +774,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -794,16 +794,16 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="F5" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -814,16 +814,16 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D6" t="s">
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -834,16 +834,16 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -854,16 +854,16 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="F8" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -874,16 +874,16 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -894,16 +894,16 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F10" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -914,16 +914,16 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>37</v>
+        <v>77</v>
       </c>
       <c r="E11" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F11" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -934,16 +934,16 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="F12" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -954,16 +954,16 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -974,16 +974,16 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="F14" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -994,16 +994,16 @@
         <v>30</v>
       </c>
       <c r="C15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E15" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1014,16 +1014,16 @@
         <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1034,16 +1034,16 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E17" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1054,16 +1054,16 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F18" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1074,16 +1074,16 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E19" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1094,16 +1094,16 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F20" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1111,59 +1111,59 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="C21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>31</v>
+        <v>76</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F22" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F23" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AA9A7A5-A7CA-F045-ACED-36F1F6D6994E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7955B68B-B0DB-684F-96C2-A848DA9FCA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
   <si>
     <t>PaymentTerms</t>
   </si>
@@ -270,6 +270,12 @@
   </si>
   <si>
     <t>entryno, vendorno, company</t>
+  </si>
+  <si>
+    <t>no, name, company, source_system</t>
+  </si>
+  <si>
+    <t>no, name</t>
   </si>
 </sst>
 </file>
@@ -814,10 +820,10 @@
         <v>23</v>
       </c>
       <c r="C6" t="s">
-        <v>32</v>
+        <v>78</v>
       </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>79</v>
       </c>
       <c r="E6" t="s">
         <v>42</v>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7955B68B-B0DB-684F-96C2-A848DA9FCA04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B43A7BF-BE7B-F44C-AA45-ED4DDE97D0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -817,7 +817,7 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
         <v>78</v>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B43A7BF-BE7B-F44C-AA45-ED4DDE97D0AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C11351F-E580-8742-A799-4B0ACE353728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -164,30 +164,6 @@
     <t>document no,  line no.</t>
   </si>
   <si>
-    <t>accounttype, globaldimenson1code, globaldimenson2code, accountcategory</t>
-  </si>
-  <si>
-    <t>glaccountno,documenttype, globaldimenson1code, globaldimenson2code, sourcecode,sourcetype</t>
-  </si>
-  <si>
-    <t>city, postcode, globaldimenson1code, globaldimenson2code, customerpostinggroup, customerpricinggroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
-  </si>
-  <si>
-    <t>customerno, documenttype, selltocustomerno, customerpostinggroup, globaldimenson1code, globaldimenson2code, salespersoncode, sourcecode,  balaccounttype, balaccountno</t>
-  </si>
-  <si>
-    <t>city, postcode, globaldimenson1code, globaldimenson2code, vendorpostinggroup, currencycode, languagecode, paymenttermscode, purchasercode, shipmentmethodcode, shippingagentcode,  paytovendorno, paymentmethodcode, countryregioncode</t>
-  </si>
-  <si>
-    <t>documenttype, vendorno,  buyfromvendorno, globaldimenson1code, globaldimenson2code, purchasercode, sourcecode, balaccounttype</t>
-  </si>
-  <si>
-    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimenson1code, globaldimenson2code, flusingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
-  </si>
-  <si>
-    <t>itemno, entrytype, sourceno, locationcode,  globaldimenson1code, globaldimenson2code,  shptmethodcode, sourcetype, unitofmeasure, itemtracking, packageno</t>
-  </si>
-  <si>
     <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimenson1code shortcutdimenson2code, customerpostinggroup,  currencycode, customerpricinggroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostingroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaytermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
   </si>
   <si>
@@ -276,6 +252,30 @@
   </si>
   <si>
     <t>no, name</t>
+  </si>
+  <si>
+    <t>accounttype, globaldimension1code, globaldimension2code, accountcategory</t>
+  </si>
+  <si>
+    <t>glaccountno,documenttype, globaldimension1code, globaldimension2code, sourcecode,sourcetype</t>
+  </si>
+  <si>
+    <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricinggroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
+  </si>
+  <si>
+    <t>customerno, documenttype, selltocustomerno, customerpostinggroup, globaldimension1code, globaldimension2code, salespersoncode, sourcecode,  balaccounttype, balaccountno</t>
+  </si>
+  <si>
+    <t>city, postcode, globaldimension1code, globaldimension2code, vendorpostinggroup, currencycode, languagecode, paymenttermscode, purchasercode, shipmentmethodcode, shippingagentcode,  paytovendorno, paymentmethodcode, countryregioncode</t>
+  </si>
+  <si>
+    <t>documenttype, vendorno,  buyfromvendorno, globaldimension1code, globaldimension2code, purchasercode, sourcecode, balaccounttype</t>
+  </si>
+  <si>
+    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flusingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
+  </si>
+  <si>
+    <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, unitofmeasure, itemtracking, packageno</t>
   </si>
 </sst>
 </file>
@@ -723,19 +723,19 @@
         <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -786,10 +786,10 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -806,10 +806,10 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="F5" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -820,16 +820,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F6" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -846,10 +846,10 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>43</v>
+        <v>73</v>
       </c>
       <c r="F7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -866,10 +866,10 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="F8" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -886,10 +886,10 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="F9" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -906,10 +906,10 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>46</v>
+        <v>76</v>
       </c>
       <c r="F10" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -923,13 +923,13 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
+        <v>69</v>
+      </c>
+      <c r="E11" t="s">
         <v>77</v>
       </c>
-      <c r="E11" t="s">
-        <v>47</v>
-      </c>
       <c r="F11" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -946,10 +946,10 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>48</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -966,10 +966,10 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>49</v>
+        <v>79</v>
       </c>
       <c r="F13" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -986,10 +986,10 @@
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -1003,13 +1003,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E15" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1026,10 +1026,10 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1043,13 +1043,13 @@
         <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E17" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1066,10 +1066,10 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1083,13 +1083,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1106,10 +1106,10 @@
         <v>29</v>
       </c>
       <c r="E20" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1123,13 +1123,13 @@
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
+        <v>50</v>
+      </c>
+      <c r="F21" t="s">
         <v>58</v>
-      </c>
-      <c r="F21" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1146,10 +1146,10 @@
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1166,10 +1166,10 @@
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C11351F-E580-8742-A799-4B0ACE353728}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A432C088-5A53-E646-9D14-580BB2660455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -260,9 +260,6 @@
     <t>glaccountno,documenttype, globaldimension1code, globaldimension2code, sourcecode,sourcetype</t>
   </si>
   <si>
-    <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricinggroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
-  </si>
-  <si>
     <t>customerno, documenttype, selltocustomerno, customerpostinggroup, globaldimension1code, globaldimension2code, salespersoncode, sourcecode,  balaccounttype, balaccountno</t>
   </si>
   <si>
@@ -276,6 +273,9 @@
   </si>
   <si>
     <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, unitofmeasure, itemtracking, packageno</t>
+  </si>
+  <si>
+    <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
   </si>
 </sst>
 </file>
@@ -866,7 +866,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -886,7 +886,7 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F9" t="s">
         <v>53</v>
@@ -906,7 +906,7 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F10" t="s">
         <v>54</v>
@@ -926,7 +926,7 @@
         <v>69</v>
       </c>
       <c r="E11" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F11" t="s">
         <v>53</v>
@@ -946,7 +946,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
@@ -966,7 +966,7 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A432C088-5A53-E646-9D14-580BB2660455}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8489D8F8-DC10-5C46-9405-58A3D3059F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1460" yWindow="1500" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="5000" yWindow="920" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -269,13 +269,13 @@
     <t>documenttype, vendorno,  buyfromvendorno, globaldimension1code, globaldimension2code, purchasercode, sourcecode, balaccounttype</t>
   </si>
   <si>
-    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flusingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
-  </si>
-  <si>
     <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, unitofmeasure, itemtracking, packageno</t>
   </si>
   <si>
     <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
+  </si>
+  <si>
+    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flushingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
   </si>
 </sst>
 </file>
@@ -866,7 +866,7 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="F8" t="s">
         <v>51</v>
@@ -946,7 +946,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="F12" t="s">
         <v>55</v>
@@ -966,7 +966,7 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F13" t="s">
         <v>53</v>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8489D8F8-DC10-5C46-9405-58A3D3059F61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D381D242-6916-6B45-8202-59019E39B585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5000" yWindow="920" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="1840" yWindow="920" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
   <si>
     <t>PaymentTerms</t>
   </si>
@@ -191,36 +191,6 @@
     <t xml:space="preserve">buyfromvendorno, no,  type, locationcode, postinggroup, unitofmeasure,  shortcutdimenson1code, shortcutdimenson2code, jobno, receiptno,  orderno, paytovendorno,  vendoritemno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype,  transactiontype, transportmethod,  taxareacode, taxgroupcode,  vatbuspostinggroup, vatprodpostinggroup,  vatidentifier, dimensonsetid, jobtaskno,  jobcurrencycode, defferalcode,   allocationaccountno,  prodorderno, variantcode, bincode,  unitofmeasurecode,  fapostingtype,  depreciationbooktype, maintenancecode, insuranceno,  budgetedfano,  responsibilitycenter,  itemcategorycode,  purchasingcode, </t>
   </si>
   <si>
-    <t>company</t>
-  </si>
-  <si>
-    <t>company,  postingdate</t>
-  </si>
-  <si>
-    <t>company, postingdate</t>
-  </si>
-  <si>
-    <t>cpmpany</t>
-  </si>
-  <si>
-    <t>company, itemcategorycode</t>
-  </si>
-  <si>
-    <t>company, selltocustomerno</t>
-  </si>
-  <si>
-    <t>company, buyfromvendorno</t>
-  </si>
-  <si>
-    <t>company, no</t>
-  </si>
-  <si>
-    <t>company,  no</t>
-  </si>
-  <si>
-    <t>company, city</t>
-  </si>
-  <si>
     <t>Bronze_Source_Keys</t>
   </si>
   <si>
@@ -276,6 +246,33 @@
   </si>
   <si>
     <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flushingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
+  </si>
+  <si>
+    <t>originating_company</t>
+  </si>
+  <si>
+    <t>originating_company,  postingdate</t>
+  </si>
+  <si>
+    <t>originating_company, itemcategorycode</t>
+  </si>
+  <si>
+    <t>originating_company, postingdate</t>
+  </si>
+  <si>
+    <t>originating_company, selltocustomerno</t>
+  </si>
+  <si>
+    <t>originating_company, buyfromvendorno</t>
+  </si>
+  <si>
+    <t>originating_company,  no</t>
+  </si>
+  <si>
+    <t>originating_company, no</t>
+  </si>
+  <si>
+    <t>originating_company, city</t>
   </si>
 </sst>
 </file>
@@ -723,19 +720,19 @@
         <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>61</v>
+        <v>51</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>63</v>
+        <v>53</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -786,10 +783,10 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -806,10 +803,10 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>67</v>
-      </c>
-      <c r="F5" t="s">
-        <v>51</v>
+        <v>57</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -820,16 +817,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="D6" t="s">
-        <v>71</v>
-      </c>
-      <c r="E6" t="s">
-        <v>72</v>
-      </c>
-      <c r="F6" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -846,10 +843,10 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="F7" t="s">
-        <v>52</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -866,10 +863,10 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>78</v>
-      </c>
-      <c r="F8" t="s">
-        <v>51</v>
+        <v>68</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -886,10 +883,10 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F9" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -906,10 +903,10 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>75</v>
-      </c>
-      <c r="F10" t="s">
-        <v>54</v>
+        <v>65</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -923,13 +920,13 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="E11" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="F11" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -946,10 +943,10 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>72</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -966,10 +963,10 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>53</v>
+        <v>73</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -989,7 +986,7 @@
         <v>42</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -1003,13 +1000,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E15" t="s">
         <v>49</v>
       </c>
       <c r="F15" t="s">
-        <v>51</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1029,7 +1026,7 @@
         <v>43</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1043,13 +1040,13 @@
         <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E17" t="s">
         <v>48</v>
       </c>
       <c r="F17" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1069,7 +1066,7 @@
         <v>44</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.2">
@@ -1083,13 +1080,13 @@
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E19" t="s">
         <v>47</v>
       </c>
       <c r="F19" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.2">
@@ -1109,7 +1106,7 @@
         <v>46</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.2">
@@ -1123,13 +1120,13 @@
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E21" t="s">
         <v>50</v>
       </c>
       <c r="F21" t="s">
-        <v>58</v>
+        <v>77</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1149,7 +1146,7 @@
         <v>45</v>
       </c>
       <c r="F22" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1169,7 +1166,7 @@
         <v>45</v>
       </c>
       <c r="F23" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D381D242-6916-6B45-8202-59019E39B585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A638ED93-5CD4-774D-9547-E65555390136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1840" yWindow="920" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="-260" yWindow="-19060" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -164,33 +164,12 @@
     <t>document no,  line no.</t>
   </si>
   <si>
-    <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimenson1code shortcutdimenson2code, customerpostinggroup,  currencycode, customerpricinggroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostingroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaytermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
-  </si>
-  <si>
-    <t xml:space="preserve">documenttype, buyfromvendorno, paytovendorno,  paytocity,  shiptocode, shiptocity, paymenttermscode, locationcode,  shortcutdimenson1code, shortcutdimenson2code, vendorpostinggroup, currencycode,  purchasercode,  selltocustomerno, reasoncode, genbuspostinggroup, transactiontype, transportmethod, vatcountryregioncode,  buyfromcity, paytopostcode, paytocounty,  buyfrompostcode, buyfromcounty, shiptopostcode, shiptocounty,  shiptocountryregioncode, balaccounttype,  prepmtpaymenttermscode,  buyfromcontactno, paytocontactno, responsibilitycenter, </t>
-  </si>
-  <si>
-    <t>selltocustomerno, billtocustomerno, billtocity,  billtocontact, shiptocity,  shiptocontact, paymenttermscode,  shipmentmethodcode,  locationcode, shortcutdimenson1code, shortcutdimenson3code, customerpostinggroup,  currencycode,  salespersoncode, orderno,  genbuspostinggroup, vatcountryregioncode, transactiontype, transportmethod,  selltocity, billtopostcode, billtocountry, billtocountryregioncode, selltopostcode,  selltocounty,  shiptopostcode, shiptocounty,  shiptocountryregioncode, balaccounttype,  paymentmethodcode, shippingagentcode,  preassignedno, sourcecode,  vatbuspostinggroup,  prepaymentorderno,  dimensonsetid,  custledgerentryno, selltocontactno, billtocontactno, resonsibilitycenter</t>
-  </si>
-  <si>
     <t>contactno, city, postcode, county, countryregioncode</t>
   </si>
   <si>
-    <t xml:space="preserve">buyfromvendorno, paytovendorno, paytocity, paytocontact,   shiptocode, shiptocity, shiptocountryregioncode,  paymenttermscode,  shipmentmethodcode, locationcode, shortcutdimension1code, shortcutdimenson2code, vendorpostinggroup , currencycode,  invoicedisccode, languagecode, purchasercode, orderno, vendorinvoiceno,  selltocustomerno, reasoncode, genbuspostinggroup, transactiontype, transportmethod, vatcountryregion,  buyfromcity, buyfromcontact, paytopostcode, oaytocounty, paytocountryregioncode, buyfrompostcode, buyfromcounty, buyfromcountryregioncode,  shiptopostcode, shiptocountry, shiptocountry, balaccounttype,  paymentmethodcode,  preassignedno, sourcecode,  vatbuspostinggroup, prepaymentorderno, quoteno, creditorno, dimensonsetid,  remittocode, vendorledgerentryno, buyfromcontactno, paytocontactno, responsibilitycenter, pricecalculationmethod, </t>
-  </si>
-  <si>
-    <t>selltocustomerno,no,   type, locationcode, postinggroup,  unitofmeasure,  shortcutdimenson1code, shortcutdimenson2code, customerpricegroup, orderno, jobno,  shipmentno,  billtocustomerno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype, transactiontype, transactionmethod,  taxcategory,  vatbuspostinggroup, vatprodpostinggroup,  vatidentifier</t>
-  </si>
-  <si>
     <t xml:space="preserve">documenttype, buyfromvendorno,no , type, locationcode, postinggroup, paytovendorno, genbuspostinggroup, genprodpostinggroup,  vatcalculationtype, transactiontype, transportmethod, vatbuspostinggroup, vatprodpostinggroup, currencycode,  vatidentifier,  fapostingtype,  depreciationbookcode,  maintenancecode,  insuranceno,  budgetedfano,  responsibilitycenter, itemcategorycode </t>
   </si>
   <si>
-    <t>documenttype, selltocustomerno, no, type,  locationcode, postinggroup, unitofmeasure,  shortcutdimenson1code, shortcutdimenson2code, customerpricinggroup,  billtocustomerno,  purchaseorderno,  genbuspostinggroup,  genprodpostinggroup, vatcalculationtype,  transactiontype,  transportmethod,  taxcategory, vatbuspostinggroup, vatprodpostinggroup, currencycode, vatidentifier, prepmtvatcalctype, dimensonsetid, bincode, unitofmeasure,  itemcategorycode,  shippingagentcode,  shippingagentservicecode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">buyfromvendorno, no,  type, locationcode, postinggroup, unitofmeasure,  shortcutdimenson1code, shortcutdimenson2code, jobno, receiptno,  orderno, paytovendorno,  vendoritemno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype,  transactiontype, transportmethod,  taxareacode, taxgroupcode,  vatbuspostinggroup, vatprodpostinggroup,  vatidentifier, dimensonsetid, jobtaskno,  jobcurrencycode, defferalcode,   allocationaccountno,  prodorderno, variantcode, bincode,  unitofmeasurecode,  fapostingtype,  depreciationbooktype, maintenancecode, insuranceno,  budgetedfano,  responsibilitycenter,  itemcategorycode,  purchasingcode, </t>
-  </si>
-  <si>
     <t>Bronze_Source_Keys</t>
   </si>
   <si>
@@ -239,9 +218,6 @@
     <t>documenttype, vendorno,  buyfromvendorno, globaldimension1code, globaldimension2code, purchasercode, sourcecode, balaccounttype</t>
   </si>
   <si>
-    <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, unitofmeasure, itemtracking, packageno</t>
-  </si>
-  <si>
     <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
   </si>
   <si>
@@ -273,13 +249,113 @@
   </si>
   <si>
     <t>originating_company, city</t>
+  </si>
+  <si>
+    <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, itemtracking, packageno</t>
+  </si>
+  <si>
+    <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimension1code shortcutdimension2code, customerpostinggroup,  currencycode, customerpricegroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostinggroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaymenttermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
+  </si>
+  <si>
+    <t>documenttype, selltocustomerno, no,  type,  locationcode, postinggroup, unitofmeasure,  shortcutdimension1code, shortcutdimension2code, customerpricegroup,  billtocustomerno,  purchaseorderno,  genbuspostinggroup,  genprodpostinggroup, vatcalculationtype,  transactiontype,  transportmethod,  taxcategory, vatbuspostinggroup, vatprodpostinggroup, currencycode, vatidentifier, prepmtvatcalctype, dimensionsetid, bincode, unitofmeasure,  itemcategorycode,  shippingagentcode,  shippingagentservicecode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">documenttype, buyfromvendorno, paytovendorno,  paytocity,  shiptocode, shiptocity, paymenttermscode, locationcode,  shortcutdimension1code, shortcutdimension2code, vendorpostinggroup, currencycode,  purchasercode,  selltocustomerno, reasoncode, genbuspostinggroup, transactiontype, transportmethod, vatcountryregioncode,  buyfromcity, paytopostcode, paytocounty,  buyfrompostcode, buyfromcounty, shiptopostcode, shiptocounty,  shiptocountryregioncode, balaccounttype,  prepmtpaymenttermscode,  buyfromcontactno, paytocontactno, responsibilitycenter, </t>
+  </si>
+  <si>
+    <t xml:space="preserve">selltocustomerno, billtocustomerno, billtocity,  billtocontact, shiptocity,  shiptocontact, paymenttermscode,  shipmentmethodcode,  locationcode, shortcutdimension1code, shortcutdimension2code, customerpostinggroup,  currencycode,  salespersoncode, orderno,  genbuspostinggroup, vatcountryregioncode, transactiontype, transportmethod,  selltocity, billtopostcode, billtocounty, billtocountryregioncode, selltopostcode,  selltocounty,  shiptopostcode, shiptocounty,  shiptocountryregioncode, balaccounttype,  paymentmethodcode, shippingagentcode,  preassignedno, sourcecode,  vatbuspostinggroup,  prepaymentorderno,  dimensionsetid,  custledgerentryno, selltocontactno, billtocontactno </t>
+  </si>
+  <si>
+    <r>
+      <t>selltocustomerno,</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, locationcode, postinggroup, unitofmeasure, shortcutdimension1code, shortcutdimension2code, customerpricegroup, orderno, jobno, shipmentno, billtocustomerno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype, transactiontype, taxcategory, vatbuspostinggroup, vatprodpostinggroup, vatidentifier </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">buyfromvendorno, paytovendorno, paytocity, paytocontact, shiptocode, shiptocity, shiptocountryregioncode, paymenttermscode, shipmentmethodcode, locationcode, shortcutdimension1code, shortcutdimension2code, vendorpostinggroup , currencycode, invoicedisccode, languagecode, purchasercode, orderno, vendorinvoiceno, selltocustomerno, reasoncode, genbuspostinggroup, transactiontype, transportmethod, vatcountryregioncode, buyfromcity, buyfromcontact, paytopostcode, paytocounty, paytocountryregioncode, buyfrompostcode, buyfromcounty, buyfromcountryregioncode, shiptopostcode, shiptocounty, shiptocountryregioncode, balaccounttype, paymentmethodcode, preassignedno, sourcecode, vatbuspostinggroup, prepaymentorderno, quoteno, creditorno, dimensionsetid, remittocode, vendorledgerentryno, buyfromcontactno, paytocontactno, responsibilitycenter, pricecalculationmethod </t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">buyfromvendorno, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>no</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF0000FF"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="14"/>
+        <color rgb="FF000000"/>
+        <rFont val="Menlo"/>
+        <family val="2"/>
+      </rPr>
+      <t>, locationcode, postinggroup, unitofmeasure, shortcutdimension1code, shortcutdimension2code, jobno, receiptno, orderno, paytovendorno, vendoritemno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype, transactiontype, transportmethod, taxareacode, taxgroupcode, vatbuspostinggroup, vatprodpostinggroup, vatidentifier, dimensionsetid, jobtaskno, jobcurrencycode, deferralcode, allocationaccountno, prodorderno, variantcode, bincode, unitofmeasurecode, fapostingtype, depreciationbookcode, maintenancecode, insuranceno, budgetedfano, responsibilitycenter, itemcategorycode, purchasingcode</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -305,6 +381,18 @@
     <font>
       <sz val="12"/>
       <color rgb="FFCE9178"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Menlo"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0000FF"/>
       <name val="Menlo"/>
       <family val="2"/>
     </font>
@@ -359,7 +447,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
@@ -370,6 +458,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -720,19 +809,19 @@
         <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="E1" s="5" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>54</v>
+        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -783,10 +872,10 @@
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>56</v>
+        <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -803,10 +892,10 @@
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>57</v>
+        <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -817,16 +906,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>54</v>
       </c>
       <c r="E6" t="s">
+        <v>55</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -843,10 +932,10 @@
         <v>26</v>
       </c>
       <c r="E7" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
         <v>63</v>
-      </c>
-      <c r="F7" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -863,10 +952,10 @@
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -883,10 +972,10 @@
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -903,10 +992,10 @@
         <v>28</v>
       </c>
       <c r="E10" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -920,13 +1009,13 @@
         <v>33</v>
       </c>
       <c r="D11" t="s">
+        <v>52</v>
+      </c>
+      <c r="E11" t="s">
         <v>59</v>
       </c>
-      <c r="E11" t="s">
-        <v>66</v>
-      </c>
       <c r="F11" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -943,10 +1032,10 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="F12" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -963,10 +1052,10 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -983,10 +1072,10 @@
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>42</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -1000,13 +1089,13 @@
         <v>38</v>
       </c>
       <c r="D15" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>49</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1023,10 +1112,10 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1040,13 +1129,13 @@
         <v>38</v>
       </c>
       <c r="D17" t="s">
-        <v>58</v>
+        <v>51</v>
       </c>
       <c r="E17" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1063,13 +1152,13 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="F18" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.2">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A19" t="s">
         <v>17</v>
       </c>
@@ -1080,16 +1169,16 @@
         <v>38</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
-      </c>
-      <c r="E19" t="s">
-        <v>47</v>
+        <v>51</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>76</v>
       </c>
       <c r="F19" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.2">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -1102,14 +1191,14 @@
       <c r="D20" t="s">
         <v>29</v>
       </c>
-      <c r="E20" t="s">
-        <v>46</v>
+      <c r="E20" s="6" t="s">
+        <v>77</v>
       </c>
       <c r="F20" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.2">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
       <c r="A21" t="s">
         <v>19</v>
       </c>
@@ -1120,13 +1209,13 @@
         <v>38</v>
       </c>
       <c r="D21" t="s">
-        <v>58</v>
-      </c>
-      <c r="E21" t="s">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>78</v>
       </c>
       <c r="F21" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1143,10 +1232,10 @@
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1163,10 +1252,10 @@
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A638ED93-5CD4-774D-9547-E65555390136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E469CD-2ADF-1D4C-932B-227778ED93A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-260" yWindow="-19060" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -219,9 +219,6 @@
   </si>
   <si>
     <t>city, postcode, globaldimension1code, globaldimension2code, customerpostinggroup, customerpricegroup, languagecode, paymenttermscode, salespersoncode, shipmentmethodcode, shippingagentcode,  customerdiscgroup, countryregioncode,  billtocustomerno, locationcode, contacttype</t>
-  </si>
-  <si>
-    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flushingmethod,  salesunitofmeasure, purchaseunitofmeasure, reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
   </si>
   <si>
     <t>originating_company</t>
@@ -349,6 +346,9 @@
       </rPr>
       <t>, locationcode, postinggroup, unitofmeasure, shortcutdimension1code, shortcutdimension2code, jobno, receiptno, orderno, paytovendorno, vendoritemno, genbuspostinggroup, genprodpostinggroup, vatcalculationtype, transactiontype, transportmethod, taxareacode, taxgroupcode, vatbuspostinggroup, vatprodpostinggroup, vatidentifier, dimensionsetid, jobtaskno, jobcurrencycode, deferralcode, allocationaccountno, prodorderno, variantcode, bincode, unitofmeasurecode, fapostingtype, depreciationbookcode, maintenancecode, insuranceno, budgetedfano, responsibilitycenter, itemcategorycode, purchasingcode</t>
     </r>
+  </si>
+  <si>
+    <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flushingmethod,  salesunitofmeasure,  reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
   </si>
 </sst>
 </file>
@@ -875,7 +875,7 @@
         <v>49</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -895,7 +895,7 @@
         <v>50</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -915,7 +915,7 @@
         <v>55</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -935,7 +935,7 @@
         <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -955,7 +955,7 @@
         <v>60</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -975,7 +975,7 @@
         <v>57</v>
       </c>
       <c r="F9" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -995,7 +995,7 @@
         <v>58</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -1015,7 +1015,7 @@
         <v>59</v>
       </c>
       <c r="F11" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -1032,10 +1032,10 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="F12" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -1052,10 +1052,10 @@
         <v>37</v>
       </c>
       <c r="E13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -1072,10 +1072,10 @@
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F14" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -1092,10 +1092,10 @@
         <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F15" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1112,10 +1112,10 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1135,7 +1135,7 @@
         <v>43</v>
       </c>
       <c r="F17" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1152,10 +1152,10 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F18" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1172,10 +1172,10 @@
         <v>51</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F19" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1192,10 +1192,10 @@
         <v>29</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1212,10 +1212,10 @@
         <v>51</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F21" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1235,7 +1235,7 @@
         <v>42</v>
       </c>
       <c r="F22" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1255,7 +1255,7 @@
         <v>42</v>
       </c>
       <c r="F23" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7E469CD-2ADF-1D4C-932B-227778ED93A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C2F7B-3DF2-3F4A-A3FE-8589FBD87526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-260" yWindow="-19060" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -249,9 +249,6 @@
   </si>
   <si>
     <t>itemno, entrytype, sourceno, locationcode,  globaldimension1code, globaldimension2code,  shptmethodcode, sourcetype, itemtracking, packageno</t>
-  </si>
-  <si>
-    <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimension1code shortcutdimension2code, customerpostinggroup,  currencycode, customerpricegroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostinggroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaymenttermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
   </si>
   <si>
     <t>documenttype, selltocustomerno, no,  type,  locationcode, postinggroup, unitofmeasure,  shortcutdimension1code, shortcutdimension2code, customerpricegroup,  billtocustomerno,  purchaseorderno,  genbuspostinggroup,  genprodpostinggroup, vatcalculationtype,  transactiontype,  transportmethod,  taxcategory, vatbuspostinggroup, vatprodpostinggroup, currencycode, vatidentifier, prepmtvatcalctype, dimensionsetid, bincode, unitofmeasure,  itemcategorycode,  shippingagentcode,  shippingagentservicecode</t>
@@ -349,6 +346,9 @@
   </si>
   <si>
     <t>baseunitofmeasure,  type, inventorypostinggroup, shelfno, itemdiscgroup, vendorno, countryregionpurchasedcode,  globaldimension1code, globaldimension2code, flushingmethod,  salesunitofmeasure,  reorderingpolicy, manufacturingpolicy, itemcategorycode,  itemtrackingcode, subscriptionoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimension1code, shortcutdimension2code, customerpostinggroup,  currencycode, customerpricegroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostinggroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaymenttermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
   </si>
 </sst>
 </file>
@@ -1032,7 +1032,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F12" t="s">
         <v>63</v>
@@ -1072,7 +1072,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="F14" t="s">
         <v>65</v>
@@ -1092,7 +1092,7 @@
         <v>51</v>
       </c>
       <c r="E15" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F15" t="s">
         <v>61</v>
@@ -1112,7 +1112,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>66</v>
@@ -1152,7 +1152,7 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F18" t="s">
         <v>65</v>
@@ -1172,7 +1172,7 @@
         <v>51</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F19" t="s">
         <v>68</v>
@@ -1192,7 +1192,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="F20" t="s">
         <v>66</v>
@@ -1212,7 +1212,7 @@
         <v>51</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="F21" t="s">
         <v>68</v>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{643C2F7B-3DF2-3F4A-A3FE-8589FBD87526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76C22B4-9158-F047-8027-AD9974365B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-260" yWindow="-19060" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
@@ -128,9 +128,6 @@
     <t>no, company</t>
   </si>
   <si>
-    <t>documentNo, lineNo</t>
-  </si>
-  <si>
     <t>code, description, company, source_system</t>
   </si>
   <si>
@@ -152,16 +149,10 @@
     <t>entryno, itemno,company</t>
   </si>
   <si>
-    <t>documentno, Lineno,company, source_system</t>
-  </si>
-  <si>
     <t>Prescriber</t>
   </si>
   <si>
     <t>Facility</t>
-  </si>
-  <si>
-    <t>document no,  line no.</t>
   </si>
   <si>
     <t>contactno, city, postcode, county, countryregioncode</t>
@@ -349,6 +340,15 @@
   </si>
   <si>
     <t xml:space="preserve">documenttype, selltocustomerno, billtocustomerno, billtocity,  shiptocity, paymenttermscode, shipmentmethodcode, locationcode,  shortcutdimension1code, shortcutdimension2code, customerpostinggroup,  currencycode, customerpricegroup,  customerdiscgroup, languagecode, salespersoncode, genbuspostinggroup,  transactiontype, transportmethod,  vatcountryregioncode, selltocity,  billtopostcode, billtocounty, billtocountryregioncode, selltopostcode, selltocounty, selltocountryregioncode,  balaccounttype,  prepmtpaymenttermscode, selltocontactno, billtocontactno,  responsibilitycenter,  shippingadvice </t>
+  </si>
+  <si>
+    <t>documentno, lineno</t>
+  </si>
+  <si>
+    <t>documentno,  lineno</t>
+  </si>
+  <si>
+    <t>documentno, lineno,company, source_system</t>
   </si>
 </sst>
 </file>
@@ -806,22 +806,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="E1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>44</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="F1" s="3" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.2">
@@ -832,7 +832,7 @@
         <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D2" t="s">
         <v>25</v>
@@ -849,7 +849,7 @@
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D3" t="s">
         <v>25</v>
@@ -866,16 +866,16 @@
         <v>23</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>24</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.2">
@@ -886,16 +886,16 @@
         <v>23</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.2">
@@ -906,16 +906,16 @@
         <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="D6" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.2">
@@ -926,16 +926,16 @@
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D7" t="s">
         <v>26</v>
       </c>
       <c r="E7" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.2">
@@ -946,16 +946,16 @@
         <v>21</v>
       </c>
       <c r="C8" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
         <v>27</v>
       </c>
       <c r="E8" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.2">
@@ -966,16 +966,16 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D9" t="s">
         <v>26</v>
       </c>
       <c r="E9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.2">
@@ -986,16 +986,16 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
         <v>28</v>
       </c>
       <c r="E10" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.2">
@@ -1006,16 +1006,16 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="E11" t="s">
+        <v>56</v>
+      </c>
+      <c r="F11" t="s">
         <v>59</v>
-      </c>
-      <c r="F11" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.2">
@@ -1026,16 +1026,16 @@
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F12" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.2">
@@ -1046,16 +1046,16 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D13" t="s">
         <v>36</v>
       </c>
-      <c r="D13" t="s">
-        <v>37</v>
-      </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.2">
@@ -1066,16 +1066,16 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F14" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.2">
@@ -1083,19 +1083,19 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>30</v>
+        <v>76</v>
       </c>
       <c r="C15" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D15" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F15" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="16" spans="1:6" s="2" customFormat="1" x14ac:dyDescent="0.2">
@@ -1106,16 +1106,16 @@
         <v>21</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.2">
@@ -1126,16 +1126,16 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D17" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="F17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.2">
@@ -1146,16 +1146,16 @@
         <v>21</v>
       </c>
       <c r="C18" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D18" t="s">
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F18" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1166,16 +1166,16 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D19" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F19" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1186,16 +1186,16 @@
         <v>21</v>
       </c>
       <c r="C20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D20" t="s">
         <v>29</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F20" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1203,59 +1203,59 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>77</v>
       </c>
       <c r="C21" t="s">
-        <v>38</v>
+        <v>78</v>
       </c>
       <c r="D21" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F21" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A22" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" t="s">
         <v>21</v>
       </c>
       <c r="C22" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D22" t="s">
         <v>28</v>
       </c>
       <c r="E22" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" t="s">
         <v>21</v>
       </c>
       <c r="C23" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D23" t="s">
         <v>28</v>
       </c>
       <c r="E23" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/documentation/historical_bronze_workflow_mapping.xlsx
+++ b/documentation/historical_bronze_workflow_mapping.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/fantasysuperkick/workspace/ccg/datawarehouse/documentation/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B76C22B4-9158-F047-8027-AD9974365B1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B20D8603-F831-1B48-A954-56F1FA889E4E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-260" yWindow="-19060" windowWidth="26960" windowHeight="15940" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
+    <workbookView xWindow="660" yWindow="500" windowWidth="28140" windowHeight="17500" xr2:uid="{63FD3DF8-BE3E-CA4B-9FF3-647869DC2764}"/>
   </bookViews>
   <sheets>
     <sheet name="Historical" sheetId="2" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="136" uniqueCount="78">
   <si>
     <t>PaymentTerms</t>
   </si>
@@ -231,9 +231,6 @@
   </si>
   <si>
     <t>originating_company,  no</t>
-  </si>
-  <si>
-    <t>originating_company, no</t>
   </si>
   <si>
     <t>originating_company, city</t>
@@ -1032,7 +1029,7 @@
         <v>29</v>
       </c>
       <c r="E12" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F12" t="s">
         <v>60</v>
@@ -1052,7 +1049,7 @@
         <v>36</v>
       </c>
       <c r="E13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F13" t="s">
         <v>61</v>
@@ -1072,7 +1069,7 @@
         <v>29</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="F14" t="s">
         <v>62</v>
@@ -1083,16 +1080,16 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D15" t="s">
         <v>48</v>
       </c>
       <c r="E15" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F15" t="s">
         <v>58</v>
@@ -1112,7 +1109,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>63</v>
@@ -1126,7 +1123,7 @@
         <v>22</v>
       </c>
       <c r="C17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D17" t="s">
         <v>48</v>
@@ -1152,7 +1149,7 @@
         <v>29</v>
       </c>
       <c r="E18" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F18" t="s">
         <v>62</v>
@@ -1166,16 +1163,16 @@
         <v>22</v>
       </c>
       <c r="C19" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D19" t="s">
         <v>48</v>
       </c>
       <c r="E19" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F19" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="18" x14ac:dyDescent="0.2">
@@ -1192,7 +1189,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F20" t="s">
         <v>63</v>
@@ -1203,19 +1200,19 @@
         <v>19</v>
       </c>
       <c r="B21" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" t="s">
         <v>77</v>
-      </c>
-      <c r="C21" t="s">
-        <v>78</v>
       </c>
       <c r="D21" t="s">
         <v>48</v>
       </c>
       <c r="E21" s="6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F21" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.2">
@@ -1235,7 +1232,7 @@
         <v>39</v>
       </c>
       <c r="F22" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.2">
@@ -1255,7 +1252,7 @@
         <v>39</v>
       </c>
       <c r="F23" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
   </sheetData>
